--- a/astro_logs.xlsx
+++ b/astro_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,11 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>SessionID</t>
         </is>
       </c>
     </row>
@@ -489,6 +494,7 @@
           <t>Live Update</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -534,6 +540,139 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>Submitted</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-31 17:14:15</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Refinement User</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Live Update</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>session_A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-31 18:22:31</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Success User</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>123-456</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Earth</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>career</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Verification complete</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>session_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:07:41</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Devashish Pathak</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>+977 9847694693</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kathmandu, Nepal</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>birth-chart</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>direct_submit_190741</t>
         </is>
       </c>
     </row>

--- a/astro_logs.xlsx
+++ b/astro_logs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,6 +676,42 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:59:51</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Devashish Pathak</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+977 </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>birth-chart</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Live Update</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>session_tcli343m2_1775117671409</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
